--- a/rendered/test.plan_bom.xlsx
+++ b/rendered/test.plan_bom.xlsx
@@ -546,7 +546,7 @@
         <v>splice</v>
       </c>
       <c r="C4" t="str">
-        <v>Unassigned</v>
+        <v>Solder Splice</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -657,7 +657,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>4/21/2026, 4:39:56 PM</v>
+        <v>4/21/2026, 5:17:32 PM</v>
       </c>
     </row>
   </sheetData>
